--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -790,22 +790,22 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -815,29 +815,29 @@
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………そこまでしてくれたなら…応えるわ</t>
+          <t xml:space="preserve">…そこまで。あなたの癖、全部見えていたわ</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -847,29 +847,29 @@
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく。…期待してて</t>
+          <t xml:space="preserve">…もう結末は、最初から決まっていたの</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -879,14 +879,14 @@
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ここで、闘えるなら……</t>
+          <t xml:space="preserve">…惜しかったわね。あと一手、足りなかった</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -896,12 +896,12 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.hit[1]</t>
+          <t xml:space="preserve">competition_won.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -911,14 +911,14 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あなたたちの前では、終われないの。</t>
+          <t xml:space="preserve">………そこまでしてくれたなら…応えるわ</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -928,12 +928,12 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.hit[2]</t>
+          <t xml:space="preserve">direct.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -943,14 +943,14 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立てるわ。</t>
+          <t xml:space="preserve">………よろしく。…期待してて</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -960,12 +960,12 @@
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.win[1]</t>
+          <t xml:space="preserve">fa_signing.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -975,14 +975,14 @@
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりじゃなかったの。切った側に、見せられたわ。</t>
+          <t xml:space="preserve">………ここで、闘えるなら……</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.win[2]</t>
+          <t xml:space="preserve">quiet.seductive.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1007,110 +1007,110 @@
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あそこを出て、まだ立ってる。それだけよ。</t>
+          <t xml:space="preserve">……あなたたちの前では、終われないの。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02 タッグマッチ</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……動けない、わ</t>
+          <t xml:space="preserve">……まだ、立てるわ。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02 タッグマッチ</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……届かない</t>
+          <t xml:space="preserve">……終わりじゃなかったの。切った側に、見せられたわ。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">quiet.seductive.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02 タッグマッチ</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん</t>
+          <t xml:space="preserve">……あそこを出て、まだ立ってる。それだけよ。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
@@ -1135,14 +1135,14 @@
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…させないわ</t>
+          <t xml:space="preserve">……動けない、わ</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、よ</t>
+          <t xml:space="preserve">……届かない</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
@@ -1199,14 +1199,14 @@
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…駄目よ</t>
+          <t xml:space="preserve">……ごめん</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わせて、よ</t>
+          <t xml:space="preserve">…させないわ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
@@ -1263,14 +1263,14 @@
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…せーの…ね</t>
+          <t xml:space="preserve">…まだ、よ</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いくわ</t>
+          <t xml:space="preserve">…駄目よ</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…交代、よ</t>
+          <t xml:space="preserve">…合わせて、よ</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来たわ</t>
+          <t xml:space="preserve">…せーの…ね</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
@@ -1391,14 +1391,14 @@
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…任せて、いい</t>
+          <t xml:space="preserve">…いくわ</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
@@ -1423,14 +1423,14 @@
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{partner}、ごめんなさい。</t>
+          <t xml:space="preserve">…交代、よ</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。{partner}にも…ね。</t>
+          <t xml:space="preserve">…来たわ</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1487,14 +1487,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{partner}、ありがとう。</t>
+          <t xml:space="preserve">…任せて、いい</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1519,110 +1519,110 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{partner}と、だから…ね。</t>
+          <t xml:space="preserve">…{partner}、ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………認めない…わ</t>
+          <t xml:space="preserve">…悔しい。{partner}にも…ね。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………もう…終わりよ</t>
+          <t xml:space="preserve">…{partner}、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（涙を拭い、微笑む）…ありがとう</t>
+          <t xml:space="preserve">…{partner}と、だから…ね。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（手を差し出す）…ありがとう…ね</t>
+          <t xml:space="preserve">………認めない…わ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1679,14 +1679,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………逃がさない…わ</t>
+          <t xml:space="preserve">………もう…終わりよ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………来なさい</t>
+          <t xml:space="preserve">………（涙を拭い、微笑む）…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1743,14 +1743,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（言葉はなく、ただ見つめている）</t>
+          <t xml:space="preserve">………（手を差し出す）…ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに目を閉じ、開く）</t>
+          <t xml:space="preserve">………逃がさない…わ</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1807,14 +1807,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（鋭い目で見据える）…覚悟してね</t>
+          <t xml:space="preserve">………来なさい</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………来なさい</t>
+          <t xml:space="preserve">………（言葉はなく、ただ見つめている）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（深い呼吸）…終わらせましょう</t>
+          <t xml:space="preserve">………（静かに目を閉じ、開く）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（微笑み、構える）…ええ</t>
+          <t xml:space="preserve">………（鋭い目で見据える）…覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………次は、ないわよ</t>
+          <t xml:space="preserve">………来なさい</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………まだよ</t>
+          <t xml:space="preserve">………（深い呼吸）…終わらせましょう</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（唇を噛む）…まだよ</t>
+          <t xml:space="preserve">………（微笑み、構える）…ええ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（深い息）…でも、まだよ</t>
+          <t xml:space="preserve">………次は、ないわよ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2063,14 +2063,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（拳を握る）…次は、ないわよ</t>
+          <t xml:space="preserve">………まだよ</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateLoser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2095,14 +2095,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（相手を見つめ）…まだよ</t>
+          <t xml:space="preserve">………（唇を噛む）…まだよ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateWinner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2127,14 +2127,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………嘘…でしょう…</t>
+          <t xml:space="preserve">………（深い息）…でも、まだよ</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2159,14 +2159,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…の…？</t>
+          <t xml:space="preserve">………（拳を握る）…次は、ないわよ</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2176,29 +2176,29 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[1]</t>
+          <t xml:space="preserve">winner.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ。……ごめんなさい。</t>
+          <t xml:space="preserve">………（相手を見つめ）…まだよ</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2208,29 +2208,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[2]</t>
+          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届かなかった。悔しい。</t>
+          <t xml:space="preserve">………嘘…でしょう…</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[3]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2240,29 +2240,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[3]</t>
+          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てなかったの。次は違うわ。</t>
+          <t xml:space="preserve">………勝った…の…？</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.petition[1]</t>
+          <t xml:space="preserve">seductive_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人と、やらせてほしいの。</t>
+          <t xml:space="preserve">負けたわ。……ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.petition[2]</t>
+          <t xml:space="preserve">seductive_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるの。……あの人と、やりたい。</t>
+          <t xml:space="preserve">届かなかった。悔しい。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.petition[3]</t>
+          <t xml:space="preserve">seductive_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一度、あの人と。……いいかしら。</t>
+          <t xml:space="preserve">……勝てなかったの。次は違うわ。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.sendoff[1]</t>
+          <t xml:space="preserve">seductive_quiet.petition[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2383,14 +2383,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。……行ってくるわ。</t>
+          <t xml:space="preserve">社長。あの人と、やらせてほしいの。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.sendoff[2]</t>
+          <t xml:space="preserve">seductive_quiet.petition[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2415,14 +2415,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝するわ、社長。任せて。</t>
+          <t xml:space="preserve">お願いがあるの。……あの人と、やりたい。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.petition[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.sendoff[3]</t>
+          <t xml:space="preserve">seductive_quiet.petition[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……嬉しい。ちゃんと報告するわね。</t>
+          <t xml:space="preserve">一度、あの人と。……いいかしら。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[1]</t>
+          <t xml:space="preserve">seductive_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2479,14 +2479,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ。……ありがとう、社長。</t>
+          <t xml:space="preserve">ありがとう。……行ってくるわ。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[2]</t>
+          <t xml:space="preserve">seductive_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">報告よ。勝ってきたの。</t>
+          <t xml:space="preserve">感謝するわ、社長。任せて。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[3]</t>
+          <t xml:space="preserve">seductive_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てたわ。頷いてくれたから。</t>
+          <t xml:space="preserve">……嬉しい。ちゃんと報告するわね。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet._accept[1]</t>
+          <t xml:space="preserve">seductive_quiet.win[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2575,14 +2575,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいわよ。</t>
+          <t xml:space="preserve">勝ったわ。……ありがとう、社長。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet._accept[2]</t>
+          <t xml:space="preserve">seductive_quiet.win[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ。……来なさい。</t>
+          <t xml:space="preserve">報告よ。勝ってきたの。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_quiet.win[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet._accept[3]</t>
+          <t xml:space="preserve">seductive_quiet.win[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私で、いいのね。……受けるわ。</t>
+          <t xml:space="preserve">……勝てたわ。頷いてくれたから。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.draw[1]</t>
+          <t xml:space="preserve">seductive_quiet._accept[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お預けね。</t>
+          <t xml:space="preserve">……いいわよ。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.draw[2]</t>
+          <t xml:space="preserve">seductive_quiet._accept[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りないわ。</t>
+          <t xml:space="preserve">ふふ。……来なさい。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet._accept[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.draw[3]</t>
+          <t xml:space="preserve">seductive_quiet._accept[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ。……また、今度。</t>
+          <t xml:space="preserve">私で、いいのね。……受けるわ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[1]</t>
+          <t xml:space="preserve">seductive_quiet.draw[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……上手ね、あなた。</t>
+          <t xml:space="preserve">……お預けね。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[2]</t>
+          <t xml:space="preserve">seductive_quiet.draw[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……参ったわ。</t>
+          <t xml:space="preserve">……足りないわ。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.draw[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.lose[3]</t>
+          <t xml:space="preserve">seductive_quiet.draw[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ。……悔しい。</t>
+          <t xml:space="preserve">ふふ。……また、今度。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[1]</t>
+          <t xml:space="preserve">seductive_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ね?</t>
+          <t xml:space="preserve">……上手ね、あなた。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[2]</t>
+          <t xml:space="preserve">seductive_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ。……おやすみ。</t>
+          <t xml:space="preserve">……参ったわ。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_quiet.win[3]</t>
+          <t xml:space="preserve">seductive_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、早かったわね。</t>
+          <t xml:space="preserve">ふふ。……悔しい。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2944,29 +2944,29 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive_quiet.win[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………残るわ</t>
+          <t xml:space="preserve">……ね?</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive_quiet.win[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに頷く）…ありがとう…ね</t>
+          <t xml:space="preserve">ふふ。……おやすみ。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_quiet.win[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3008,29 +3008,29 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive_quiet.win[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………まだ…よ</t>
+          <t xml:space="preserve">……まだ、早かったわね。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">accepted.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………もう…ここまでね</t>
+          <t xml:space="preserve">…さよなら…ね</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">accepted.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残るわ。ここが、いい</t>
+          <t xml:space="preserve">…ありがとう…本当に…</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3104,29 +3104,29 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">defended.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………考えさせて</t>
+          <t xml:space="preserve">…残るわ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3136,29 +3136,29 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.seductive[1]</t>
+          <t xml:space="preserve">defended.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………条件…次第ね</t>
+          <t xml:space="preserve">…ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3168,29 +3168,29 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
+          <t xml:space="preserve">…ごめんなさい…ね</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3200,29 +3200,29 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………もう少し…あと少し…</t>
+          <t xml:space="preserve">…さよなら</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3232,29 +3232,29 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">former_champ.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何のために…戦ってるの…</t>
+          <t xml:space="preserve">………残るわ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3264,29 +3264,29 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
+          <t xml:space="preserve">………（静かに頷く）…ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3296,29 +3296,29 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………戻ってきた…わ</t>
+          <t xml:space="preserve">………まだ…よ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3328,29 +3328,29 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何も…うまくいかないわ</t>
+          <t xml:space="preserve">………もう…ここまでね</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3360,29 +3360,29 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………最高の試合…だったわ</t>
+          <t xml:space="preserve">……悔いは、ないの</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3392,29 +3392,29 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………このベルト…渡さないわ</t>
+          <t xml:space="preserve">……さよなら、ね</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3424,29 +3424,29 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
+          <t xml:space="preserve">……ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.seductive[1]</t>
+          <t xml:space="preserve">B1_young.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう…ね</t>
+          <t xml:space="preserve">………まだ、なのに…ね</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3488,29 +3488,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いよいよね</t>
+          <t xml:space="preserve">……これからだったのに…ね</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">B3_older.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて</t>
+          <t xml:space="preserve">……十分、やったわ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3552,29 +3552,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">B4_champion_injury.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">……まだ、返したくなかったの</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
@@ -3594,19 +3594,19 @@
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員ね</t>
+          <t xml:space="preserve">……残るわ。ここが、いい</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3616,29 +3616,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">raise_accept.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この景色、胸に</t>
+          <t xml:space="preserve">え……本当……？ ……ありがとう、社長。ちゃんと応えるから……。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3648,29 +3648,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">raise_negotiate_accept.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">それだけでも……嬉しいわ。ありがとう、社長……。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3680,29 +3680,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やれた。……嬉しい</t>
+          <t xml:space="preserve">……そう……。分かったわ……。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3712,29 +3712,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_open.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">………考えさせて</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">……ええ……分かったわ……。……ごめんなさい、困らせて……。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3776,29 +3776,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">……聞いてくれるの……。{record}わたし……ここにいる意味が、分からなくなって……。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3808,29 +3808,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">……社長。{tenure}言いにくいんだけど……もう、ここを出たいの……。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3840,29 +3840,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">……ごめんなさい……。{tenure}わたしがいなくても……何も変わらないでしょう……。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3872,29 +3872,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}……お世話になったわ。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3904,29 +3904,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+          <t xml:space="preserve">……ごめんなさい……。嬉しいけれど……もう、決めたことなの……。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3936,29 +3936,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+          <t xml:space="preserve">えっ……そこまでしてくれるの……？ ……もう少しだけ、いてみようかしら……。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3968,29 +3968,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.seductive[1]</t>
+          <t xml:space="preserve">start.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+          <t xml:space="preserve">………条件…次第ね</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4000,29 +4000,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,29 +4032,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰。…来なよ</t>
+          <t xml:space="preserve">………もう少し…あと少し…</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4064,29 +4064,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+          <t xml:space="preserve">………何のために…戦ってるの…</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4096,29 +4096,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4128,29 +4128,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+          <t xml:space="preserve">………戻ってきた…わ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,29 +4160,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">defeat.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+          <t xml:space="preserve">………何も…うまくいかないわ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,29 +4192,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[2]</t>
+          <t xml:space="preserve">bestMatch.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+          <t xml:space="preserve">………最高の試合…だったわ</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,29 +4224,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.seductive[1]</t>
+          <t xml:space="preserve">champion.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+          <t xml:space="preserve">………このベルト…渡さないわ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4256,29 +4256,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.seductive[2]</t>
+          <t xml:space="preserve">hallOfFame.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4288,29 +4288,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.seductive[1]</t>
+          <t xml:space="preserve">mvp.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+          <t xml:space="preserve">………ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4320,29 +4320,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.seductive[2]</t>
+          <t xml:space="preserve">quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+          <t xml:space="preserve">…いよいよね</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4352,29 +4352,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くわよ</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[3]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4384,29 +4384,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.seductive[3]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+          <t xml:space="preserve">……(静かに微笑む)</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
@@ -4426,49 +4426,2129 @@
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+          <t xml:space="preserve">…満員ね</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この景色、胸に</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[3]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……(静かに微笑む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">E1.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">E1.accept.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……やれた。……嬉しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………よろしく、ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……よ、よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく、ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……待っててね</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftInterest.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………よろしく、ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftJoin.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……よ、よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく、ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……待っててね</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今は…一人に、して</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今は…一人に、して</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、終わりね</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……遠くなったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……気づけば、隣にいないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……私の光。それだけなの</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、考えないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……考えてしまうの。どうしても</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そのことばかり考えているわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここにいたいの。ずっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この場所を、守りたいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、何も感じないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……相手は誰。…来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………行くわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.quiet.seductive[1]</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr" s="12">
+      <c r="D193" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.quiet.seductive[1]</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr" s="2">
+      <c r="E193" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr" s="3">
+      <c r="F193" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">………終わった…わね。…ありがとう</t>
         </is>
       </c>
     </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H130"/>
+  <autoFilter ref="A1:H195"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -342,7 +342,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -357,7 +357,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -389,7 +389,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -421,7 +421,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.quiet[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -453,7 +453,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.quiet[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -485,7 +485,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -517,7 +517,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -613,7 +613,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -645,7 +645,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -741,7 +741,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -773,7 +773,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -805,7 +805,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -837,7 +837,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[2]</t>
+          <t xml:space="preserve">winner.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet.seductive[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[3]</t>
+          <t xml:space="preserve">winner.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -901,7 +901,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -965,7 +965,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.quiet.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.quiet.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.quiet.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.quiet.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.quiet.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.quiet.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.quiet.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.quiet.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateLoser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.quiet.seductive[1]</t>
+          <t xml:space="preserve">fateWinner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2166,7 +2166,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2198,7 +2198,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2230,7 +2230,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3030,7 +3030,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.seductive[2]</t>
+          <t xml:space="preserve">accepted.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3094,7 +3094,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3126,7 +3126,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.seductive[2]</t>
+          <t xml:space="preserve">defended.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.seductive[2]</t>
+          <t xml:space="preserve">defense_failed.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3222,7 +3222,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3254,7 +3254,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.quiet.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるの……。{record}わたし……ここにいる意味が、分からなくなって……。</t>
+          <t xml:space="preserve">……ごめんなさい。もう、限界なの。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。{tenure}言いにくいんだけど……もう、ここを出たいの……。</t>
+          <t xml:space="preserve">……ずっと黙って耐えてきたわ。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.seductive[2]</t>
+          <t xml:space="preserve">transfer_listen.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。{tenure}わたしがいなくても……何も変わらないでしょう……。</t>
+          <t xml:space="preserve">……聞いてくれるの……。{record}わたし……ここにいる意味が、分からなくなって……。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}……お世話になったわ。</t>
+          <t xml:space="preserve">……社長。{tenure}言いにくいんだけど……もう、ここを出たいの……。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。嬉しいけれど……もう、決めたことなの……。</t>
+          <t xml:space="preserve">……ごめんなさい……。{tenure}わたしがいなくても……何も変わらないでしょう……。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ……そこまでしてくれるの……？ ……もう少しだけ、いてみようかしら……。</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}……お世話になったわ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………条件…次第ね</t>
+          <t xml:space="preserve">……ごめんなさい……。嬉しいけれど……もう、決めたことなの……。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4000,29 +4000,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
+          <t xml:space="preserve">えっ……そこまでしてくれるの……？ ……もう少しだけ、いてみようかしら……。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,29 +4032,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">start.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………もう少し…あと少し…</t>
+          <t xml:space="preserve">………条件…次第ね</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4064,29 +4064,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何のために…戦ってるの…</t>
+          <t xml:space="preserve">…社長、私たちのこと…たまには思い出してくれる?</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4096,29 +4096,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
+          <t xml:space="preserve">…社長、次のメイン、私で行ってもいい?</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4128,29 +4128,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………戻ってきた…わ</t>
+          <t xml:space="preserve">…社長、待遇の話…してもいい?</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,29 +4160,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何も…うまくいかないわ</t>
+          <t xml:space="preserve">…社長、私のこと、見ていてくれてる?</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,29 +4192,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………最高の試合…だったわ</t>
+          <t xml:space="preserve">…ありがとうございます。…見てくれてたんですね、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,29 +4224,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………このベルト…渡さないわ</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4256,29 +4256,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4288,29 +4288,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう…ね</t>
+          <t xml:space="preserve">…ありがとうございます。…ちゃんと応えますね。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4320,29 +4320,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いよいよね</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4352,29 +4352,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4384,29 +4384,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">…ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員ね</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4448,29 +4448,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この景色、胸に</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.seductive[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4480,29 +4480,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[3]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4512,29 +4512,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4544,29 +4544,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やれた。……嬉しい</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4576,29 +4576,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…はい、…悪気はなかったんです。次は、声、かけます。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4608,29 +4608,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4672,29 +4672,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4704,29 +4704,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">…はい、わかりました。…やりすぎたかな。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4736,29 +4736,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4768,29 +4768,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">…ごめんなさい。…明日から、出ます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4800,29 +4800,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+          <t xml:space="preserve">…ありがとうございます。…優しい。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4832,29 +4832,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4864,29 +4864,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4896,29 +4896,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">…はい、平気です。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4928,29 +4928,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえる、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4960,29 +4960,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4992,29 +4992,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5024,29 +5024,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5056,29 +5056,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5088,29 +5088,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">（…黙って、髪に触れた）</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5120,29 +5120,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5152,29 +5152,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">…はい、…加減します。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5184,29 +5184,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+          <t xml:space="preserve">…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5216,29 +5216,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界近かったかも。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.seductive</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5248,29 +5248,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.attack.seductive</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">……もう、戻れないの</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.seductive</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5280,29 +5280,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">quiet.defend.seductive</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">あなたが望むなら</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5312,29 +5312,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5344,29 +5344,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、終わりね</t>
+          <t xml:space="preserve">………もう少し…あと少し…</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5376,29 +5376,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠くなったわ</t>
+          <t xml:space="preserve">………何のために…戦ってるの…</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5408,29 +5408,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気づけば、隣にいないの</t>
+          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5440,29 +5440,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+          <t xml:space="preserve">………戻ってきた…わ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5472,29 +5472,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の光。それだけなの</t>
+          <t xml:space="preserve">………何も…うまくいかないわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5504,29 +5504,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
+          <t xml:space="preserve">………最高の試合…だったわ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5536,29 +5536,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、考えないわ</t>
+          <t xml:space="preserve">………このベルト…渡さないわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5568,29 +5568,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
+          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5600,29 +5600,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えてしまうの。どうしても</t>
+          <t xml:space="preserve">………ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,29 +5632,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
+          <t xml:space="preserve">…いよいよね</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,29 +5696,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのことばかり考えているわ</t>
+          <t xml:space="preserve">……(静かに微笑む)</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,29 +5728,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
+          <t xml:space="preserve">…満員ね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
+          <t xml:space="preserve">…この景色、胸に</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5792,29 +5792,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたいの。ずっと</t>
+          <t xml:space="preserve">……(静かに微笑む)</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,29 +5824,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を、守りたいわ</t>
+          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,29 +5856,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
+          <t xml:space="preserve">……やれた。……嬉しい</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,29 +5888,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、何も感じないわ</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,29 +5920,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
+          <t xml:space="preserve">……よ、よろしく</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,29 +5952,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,29 +5984,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,29 +6016,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,29 +6048,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰。…来なよ</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,29 +6080,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.seductive[2]</t>
+          <t xml:space="preserve">draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+          <t xml:space="preserve">……よ、よろしく</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.seductive[2]</t>
+          <t xml:space="preserve">faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6176,29 +6176,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,29 +6208,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.seductive[2]</t>
+          <t xml:space="preserve">injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6240,29 +6240,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.seductive[1]</t>
+          <t xml:space="preserve">release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,29 +6272,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.seductive[2]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,29 +6304,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,29 +6336,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.seductive[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6368,29 +6368,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くわよ</t>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,29 +6400,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+          <t xml:space="preserve">……今は…一人に、して</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,29 +6432,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,29 +6464,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,29 +6496,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,27 +6528,1339 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今は…一人に、して</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、終わりね</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……遠くなったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……気づけば、隣にいないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……私の光。それだけなの</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、考えないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……考えてしまうの。どうしても</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そのことばかり考えているわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここにいたいの。ずっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この場所を、守りたいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、何も感じないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……相手は誰。…来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………行くわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr" s="2">
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr" s="3">
+      <c r="F236" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H195"/>
+  <autoFilter ref="A1:H236"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ね?</t>
+          <t xml:space="preserve">……ね？</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え……本当……？ ……ありがとう、社長。ちゃんと応えるから……。</t>
+          <t xml:space="preserve">ふふ……そう。……ありがとう、社長。ちゃんと応えてあげる……。</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ……分かったわ……。……ごめんなさい、困らせて……。</t>
+          <t xml:space="preserve">……ええ……分かったわ……。……今の話は、忘れてちょうだい……。</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるの……。{record}わたし……ここにいる意味が、分からなくなって……。</t>
+          <t xml:space="preserve">……聞いてくれるの……。{record}私……ここにいる意味が、分からなくなって……。</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。{tenure}わたしがいなくても……何も変わらないでしょう……。</t>
+          <t xml:space="preserve">……聞いてほしいの……。{tenure}ここを出ることに決めたわ……。もう、覆らない……。</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ……そこまでしてくれるの……？ ……もう少しだけ、いてみようかしら……。</t>
+          <t xml:space="preserve">……ふふ、そこまでするのね……。……いいわ。もう少しだけ、いてあげる……。</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちのこと…たまには思い出してくれる?</t>
+          <t xml:space="preserve">…社長、私たちのこと…たまには思い出してくれる？</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、次のメイン、私で行ってもいい?</t>
+          <t xml:space="preserve">…社長、次のメイン、私で行ってもいい？</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、待遇の話…してもいい?</t>
+          <t xml:space="preserve">…社長、待遇の話…してもいい？</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私のこと、見ていてくれてる?</t>
+          <t xml:space="preserve">…社長、私のこと、見ていてくれてる？</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………最高の試合…だったわ</t>
+          <t xml:space="preserve">仲間のために勝てて、うれしいわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………このベルト…渡さないわ</t>
+          <t xml:space="preserve">………最高の試合…だったわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
+          <t xml:space="preserve">………このベルト…渡さないわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.quiet[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう…ね</t>
+          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5647,14 +5647,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いよいよね</t>
+          <t xml:space="preserve">………ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて</t>
+          <t xml:space="preserve">相棒となら、もっと高く行けるわ。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[3]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">…いよいよね</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員ね</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[2]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この景色、胸に</t>
+          <t xml:space="preserve">……（静かに微笑む）</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[3]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに微笑む)</t>
+          <t xml:space="preserve">…満員ね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,29 +5824,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
+          <t xml:space="preserve">…この景色、胸に</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,29 +5856,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やれた。……嬉しい</t>
+          <t xml:space="preserve">……（静かに微笑む）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,29 +5888,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,29 +5920,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">……やれた。……嬉しい</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,14 +6095,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よ、よろしく</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6127,14 +6127,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6159,14 +6159,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.quiet[1]</t>
+          <t xml:space="preserve">faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
+          <t xml:space="preserve">…お世話になりました（ふっと目を伏せて）</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました(ふっと目を伏せて)</t>
+          <t xml:space="preserve">……今は…一人に、して</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">…お世話になりました（ふっと目を伏せて）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6656,29 +6656,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、終わりね</t>
+          <t xml:space="preserve">……今は…一人に、して</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6688,29 +6688,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠くなったわ</t>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気づけば、隣にいないの</t>
+          <t xml:space="preserve">……もう、終わりね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+          <t xml:space="preserve">……遠くなったわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の光。それだけなの</t>
+          <t xml:space="preserve">……気づけば、隣にいないの</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
+          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、考えないわ</t>
+          <t xml:space="preserve">……私の光。それだけなの</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
+          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えてしまうの。どうしても</t>
+          <t xml:space="preserve">……もう、考えないわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
+          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
+          <t xml:space="preserve">……考えてしまうの。どうしても</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのことばかり考えているわ</t>
+          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
+          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
+          <t xml:space="preserve">……そのことばかり考えているわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたいの。ずっと</t>
+          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を、守りたいわ</t>
+          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
+          <t xml:space="preserve">……ここにいたいの。ずっと</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、何も感じないわ</t>
+          <t xml:space="preserve">……この場所を、守りたいわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
+          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+          <t xml:space="preserve">……もう、何も感じないわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7296,29 +7296,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7328,29 +7328,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰。…来なよ</t>
+          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……相手は誰。…来なさい</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なさい</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くわよ</t>
+          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+          <t xml:space="preserve">………行くわよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,29 +7776,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
@@ -7818,49 +7818,113 @@
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居場所ができたのね。…助かるわ</t>
+          <t xml:space="preserve">………勝った…わ。…団体のために</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr" s="2">
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr" s="12">
+      <c r="D238" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr" s="2">
+      <c r="E238" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr" s="3">
+      <c r="F238" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H236"/>
+  <autoFilter ref="A1:H238"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……そう。……ありがとう、社長。ちゃんと応えてあげる……。</t>
+          <t xml:space="preserve">……ええ。……値札が変わるだけ。……中身は、そのまま。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">それだけでも……嬉しいわ。ありがとう、社長……。</t>
+          <t xml:space="preserve">……据え置き。……ふふ。……借りは、リングで返すわ。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう……。分かったわ……。</t>
+          <t xml:space="preserve">……ふふ。落ちるものは、落ちる。……それだけのこと。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………考えさせて</t>
+          <t xml:space="preserve">……そう。……そこまで。……ふふ。……もう、笑えないわね。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ……分かったわ……。……今の話は、忘れてちょうだい……。</t>
+          <t xml:space="preserve">……ええ。……納得ずく。……これで、清々したわ。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。もう、限界なの。……さようなら。</t>
+          <t xml:space="preserve">……据え置き。……理由が要るわね。……作るわ、こちらで。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.quiet[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと黙って耐えてきたわ。でも、もう……。</t>
+          <t xml:space="preserve">……下げていいわ。……盛りは過ぎた。……見えているもの、自分でも。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.quiet[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるの……。{record}私……ここにいる意味が、分からなくなって……。</t>
+          <t xml:space="preserve">ふふ……そう。……ありがとう、社長。ちゃんと応えてあげる……。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。{tenure}言いにくいんだけど……もう、ここを出たいの……。</t>
+          <t xml:space="preserve">それだけでも……嬉しいわ。ありがとう、社長……。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.quiet[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてほしいの……。{tenure}ここを出ることに決めたわ……。もう、覆らない……。</t>
+          <t xml:space="preserve">……そう……。分かったわ……。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.quiet[1]</t>
+          <t xml:space="preserve">raise_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}……お世話になったわ。</t>
+          <t xml:space="preserve">………考えさせて</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.quiet[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。嬉しいけれど……もう、決めたことなの……。</t>
+          <t xml:space="preserve">……ええ……分かったわ……。……今の話は、忘れてちょうだい……。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふふ、そこまでするのね……。……いいわ。もう少しだけ、いてあげる……。</t>
+          <t xml:space="preserve">……ごめんなさい。もう、限界なの。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.seductive.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………条件…次第ね</t>
+          <t xml:space="preserve">……ずっと黙って耐えてきたわ。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4064,29 +4064,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちのこと…たまには思い出してくれる？</t>
+          <t xml:space="preserve">……聞いてくれるの……。{record}私……ここにいる意味が、分からなくなって……。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4096,29 +4096,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、次のメイン、私で行ってもいい？</t>
+          <t xml:space="preserve">……社長。{tenure}言いにくいんだけど……もう、ここを出たいの……。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4128,29 +4128,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、待遇の話…してもいい？</t>
+          <t xml:space="preserve">……聞いてほしいの……。{tenure}ここを出ることに決めたわ……。もう、覆らない……。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,29 +4160,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私のこと、見ていてくれてる？</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}……お世話になったわ。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,29 +4192,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見てくれてたんですね、嬉しい。</t>
+          <t xml:space="preserve">……ごめんなさい……。嬉しいけれど……もう、決めたことなの……。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,29 +4224,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">……ふふ、そこまでするのね……。……いいわ。もう少しだけ、いてあげる……。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4256,29 +4256,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">start.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
+          <t xml:space="preserve">………条件…次第ね</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…ちゃんと応えますね。</t>
+          <t xml:space="preserve">…社長、私たちのこと…たまには思い出してくれる？</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…社長、次のメイン、私で行ってもいい？</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
+          <t xml:space="preserve">…社長、待遇の話…してもいい？</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…嬉しい、です。</t>
+          <t xml:space="preserve">…社長、私のこと、見ていてくれてる？</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…見てくれてたんですね、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…ちゃんと応えますね。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…悪気はなかったんです。次は、声、かけます。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…気をつけます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。…やりすぎたかな。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。…明日から、出ます。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…優しい。</t>
+          <t xml:space="preserve">…はい、…悪気はなかったんです。次は、声、かけます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4879,14 +4879,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、平気です。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえる、嬉しい。</t>
+          <t xml:space="preserve">…はい、わかりました。…やりすぎたかな。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…気をつけます。</t>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ごめんなさい。…明日から、出ます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、嬉しい。</t>
+          <t xml:space="preserve">…ありがとうございます。…優しい。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…黙って、髪に触れた）</t>
+          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
+          <t xml:space="preserve">…はい、平気です。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…加減します。</t>
+          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえる、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…続けます。</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子、限界近かったかも。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、戻れないの</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが望むなら</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5312,29 +5312,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
+          <t xml:space="preserve">（…黙って、髪に触れた）</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5344,29 +5344,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………もう少し…あと少し…</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくれるんですね。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5376,29 +5376,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何のために…戦ってるの…</t>
+          <t xml:space="preserve">…はい、…加減します。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5408,29 +5408,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
+          <t xml:space="preserve">…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5440,29 +5440,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………戻ってきた…わ</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界近かったかも。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.seductive</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5472,29 +5472,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.quiet[1]</t>
+          <t xml:space="preserve">quiet.attack.seductive</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………何も…うまくいかないわ</t>
+          <t xml:space="preserve">……もう、戻れないの</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.seductive</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5504,29 +5504,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.quiet[1]</t>
+          <t xml:space="preserve">quiet.defend.seductive</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間のために勝てて、うれしいわ。</t>
+          <t xml:space="preserve">あなたが望むなら</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5536,29 +5536,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………最高の試合…だったわ</t>
+          <t xml:space="preserve">………（静かに拳を見つめ）…変わってきたわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5568,29 +5568,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………このベルト…渡さないわ</t>
+          <t xml:space="preserve">………もう少し…あと少し…</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5600,29 +5600,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
+          <t xml:space="preserve">………何のために…戦ってるの…</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,29 +5632,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう…ね</t>
+          <t xml:space="preserve">………思い出した…わ。戦う理由</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒となら、もっと高く行けるわ。</t>
+          <t xml:space="preserve">………戻ってきた…わ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,29 +5696,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">defeat.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いよいよね</t>
+          <t xml:space="preserve">………何も…うまくいかないわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[2]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて</t>
+          <t xml:space="preserve">仲間のために勝てて、うれしいわ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[3]</t>
+          <t xml:space="preserve">bestMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに微笑む）</t>
+          <t xml:space="preserve">………最高の試合…だったわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員ね</t>
+          <t xml:space="preserve">………このベルト…渡さないわ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[2]</t>
+          <t xml:space="preserve">hallOfFame.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この景色、胸に</t>
+          <t xml:space="preserve">………（涙を堪え）…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[3]</t>
+          <t xml:space="preserve">mvp.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに微笑む）</t>
+          <t xml:space="preserve">………ありがとう…ね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,29 +5888,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.quiet[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
+          <t xml:space="preserve">相棒となら、もっと高く行けるわ。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,29 +5920,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やれた。……嬉しい</t>
+          <t xml:space="preserve">…いよいよね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,29 +5952,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,29 +5984,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……（静かに微笑む）</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
@@ -6026,19 +6026,19 @@
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">…満員ね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,29 +6048,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">…この景色、胸に</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.quiet[3]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,29 +6080,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[3]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">……（静かに微笑む）</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.quiet[1]</t>
+          <t xml:space="preserve">E1.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしく、ね</t>
+          <t xml:space="preserve">…出演の話…？ …やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.quiet[1]</t>
+          <t xml:space="preserve">E1.accept.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……やれた。……嬉しい</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく、ね</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……待っててね</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました（ふっと目を伏せて）</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、よろしくね</t>
+          <t xml:space="preserve">………よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.quiet[1]</t>
+          <t xml:space="preserve">faSigning.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">…よろしく、ね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">…よろしく。仲良くしましょ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.quiet[1]</t>
+          <t xml:space="preserve">injury.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">……待っててね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">release.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6550,7 +6550,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6582,7 +6582,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
+          <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人に、して</t>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
+          <t xml:space="preserve">……今は…一人に、して</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6720,29 +6720,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、終わりね</t>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,29 +6752,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠くなったわ</t>
+          <t xml:space="preserve">…お世話になりました（ふっと目を伏せて）</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6784,29 +6784,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気づけば、隣にいないの</t>
+          <t xml:space="preserve">…短い間だけど、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6816,29 +6816,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
+          <t xml:space="preserve">………（乱れた髪をかき上げて、笑おうとして失敗する）</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6848,29 +6848,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の光。それだけなの</t>
+          <t xml:space="preserve">………（ベルトを撫でながら、目を細めている）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
+          <t xml:space="preserve">……今は…一人に、して</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6912,29 +6912,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、考えないわ</t>
+          <t xml:space="preserve">………（ベルトに頬を寄せている）</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
+          <t xml:space="preserve">……もう、終わりね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えてしまうの。どうしても</t>
+          <t xml:space="preserve">……遠くなったわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
+          <t xml:space="preserve">……気づけば、隣にいないの</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
+          <t xml:space="preserve">一緒にいると……なんだか温かいの</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのことばかり考えているわ</t>
+          <t xml:space="preserve">……私の光。それだけなの</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
+          <t xml:space="preserve">……そばにいてくれるなら、それだけでいいわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
+          <t xml:space="preserve">……もう、考えないわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたいの。ずっと</t>
+          <t xml:space="preserve">……風が止んだ。そんな感じなの</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を、守りたいわ</t>
+          <t xml:space="preserve">……考えてしまうの。どうしても</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
+          <t xml:space="preserve">……燃えているわ。私の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、何も感じないわ</t>
+          <t xml:space="preserve">……認めたくないけど、意識してるの</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
+          <t xml:space="preserve">……そのことばかり考えているわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+          <t xml:space="preserve">……あの人がいる限り、リングに立ち続けるわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,29 +7360,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+          <t xml:space="preserve">……言葉はいらないの。リングの上で語り合いましょう</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,29 +7392,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+          <t xml:space="preserve">……ここにいたいの。ずっと</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,29 +7424,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰。…来なさい</t>
+          <t xml:space="preserve">……この場所を、守りたいわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7456,29 +7456,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+          <t xml:space="preserve">……（無言で荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,29 +7488,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.seductive[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なさい</t>
+          <t xml:space="preserve">……もう、何も感じないわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7520,29 +7520,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">trust_below_35.quiet.seductive[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきたわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,29 +7552,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+          <t xml:space="preserve">……相手は誰。…来なさい</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なさい</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くわよ</t>
+          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7840,29 +7840,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7872,59 +7872,283 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………行くわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr" s="2">
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr" s="12">
+      <c r="D245" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr" s="2">
+      <c r="E245" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr" s="3">
+      <c r="F245" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H238"/>
+  <autoFilter ref="A1:H245"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7318,7 +7318,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
+          <t xml:space="preserve">……届かなかった。でも、見えた</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,29 +7360,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
+          <t xml:space="preserve">……獲った</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,29 +7392,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
+          <t xml:space="preserve">……負けた</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,29 +7424,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰。…来なさい</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7456,29 +7456,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
+          <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
+          <t xml:space="preserve">………終わったわね。…でもまだよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なさい</t>
+          <t xml:space="preserve">……ぼろぼろ。でも、最後に立つの</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
+          <t xml:space="preserve">preFinal.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
+          <t xml:space="preserve">……まだ終わらない。最後まで、いくわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[1]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
+          <t xml:space="preserve">……相手は誰。…来なさい</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.quiet[2]</t>
+          <t xml:space="preserve">preMatch.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
+          <t xml:space="preserve">……まだ、これから。楽しませてよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
+          <t xml:space="preserve">……一人、落としたわ。まだ立ってる。……次、来なさい</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
+          <t xml:space="preserve">survivor.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
+          <t xml:space="preserve">……息、荒いけど。まだ、終わらない</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
+          <t xml:space="preserve">champion.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
+          <t xml:space="preserve">……三人で掴んだ夜。忘れないわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
+          <t xml:space="preserve">champion.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
+          <t xml:space="preserve">……一人じゃこの景色は見られなかった。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くわよ</t>
+          <t xml:space="preserve">……これだけじゃ、満たされないの。次はもっと</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">defiant.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+          <t xml:space="preserve">……物足りないわ。次は、全部もらいに行く</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+          <t xml:space="preserve">……まだ立ってるわ。ちょっと、息が荒いけどね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7840,29 +7840,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.quiet[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+          <t xml:space="preserve">……何人倒したかな。覚えてないの。でも、最後はこっち</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
@@ -7882,49 +7882,177 @@
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+          <t xml:space="preserve">………行くわよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………獲ったわ。…この舞台で</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………勝った…わ。…団体のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………終わった…わね。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここが新しい場所ね。……ええ、悪くない……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr" s="2">
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr" s="12">
+      <c r="D242" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.quiet[1]</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr" s="2">
+      <c r="E242" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr" s="3">
+      <c r="F242" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……見つかっちゃった。…ふふ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H238"/>
+  <autoFilter ref="A1:H242"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×寡黙.xlsx
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人と、やらせてほしいの。</t>
+          <t xml:space="preserve">社長。三人で、あちらへ行かせてほしいの。</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるの。……あの人と、やりたい。</t>
+          <t xml:space="preserve">お願いがあるの。……三人で、あの団体へ。</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一度、あの人と。……いいかしら。</t>
+          <t xml:space="preserve">一度、三人であちらへ。……いいかしら。</t>
         </is>
       </c>
     </row>
